--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -39,102 +39,102 @@
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
+    <t xml:space="preserve">Nancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumanque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostazal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requínoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coltauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chépica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Navidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Litueche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pumanque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marchigüe</t>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimbarongo</t>
   </si>
   <si>
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Coinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requínoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coltauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peralillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nancagua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peumo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">Chimbarongo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chépica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paredones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rengo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mostazal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graneros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rancagua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.73</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="3">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6205</v>
+        <v>6305</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23.54</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="4">
@@ -608,13 +608,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6203</v>
+        <v>6309</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21.76</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="5">
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6309</v>
+        <v>6102</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.61</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6204</v>
+        <v>6307</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.51</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +659,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13.92</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.48</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6107</v>
+        <v>6203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="10">
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6102</v>
+        <v>6110</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.32</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6116</v>
+        <v>6103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.89</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6308</v>
+        <v>6116</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8.73</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6104</v>
+        <v>6308</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8.03</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6307</v>
+        <v>6104</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6.9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6305</v>
+        <v>6302</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.33</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6113</v>
+        <v>6114</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6108</v>
+        <v>6205</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.56</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6304</v>
+        <v>6111</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.52</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6303</v>
+        <v>6106</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.27</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6302</v>
+        <v>6117</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.11</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6206</v>
+        <v>6310</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3.85</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6109</v>
+        <v>6301</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3.17</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6114</v>
+        <v>6109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2.97</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6306</v>
+        <v>6303</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2.57</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6110</v>
+        <v>6201</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2.55</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2.52</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2.43</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6117</v>
+        <v>6101</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2.41</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6106</v>
+        <v>6112</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.93</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6112</v>
+        <v>6108</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1.4</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6310</v>
+        <v>6306</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.95</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6301</v>
+        <v>6206</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.14</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="34">
@@ -1118,13 +1118,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6101</v>
+        <v>6304</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-3.82</v>
+        <v>-3.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.79</v>
+        <v>87.93</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.62</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.72</v>
+        <v>37.17</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.65</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.93</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.9</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="8">
@@ -682,7 +682,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.39</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.32</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.22</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.06</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="13">
@@ -767,7 +767,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.97</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.73</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.86</v>
+        <v>8.63</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.83</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="18">
@@ -852,7 +852,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.78</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +869,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.72</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="20">
@@ -886,7 +886,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.68</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="21">
@@ -903,7 +903,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.65</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="22">
@@ -920,7 +920,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.57</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.54</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.47</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.32</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="26">
@@ -988,7 +988,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.21</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="27">
@@ -1005,7 +1005,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.08</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.44</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.83</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1.08</v>
+        <v>-10.76</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1.37</v>
+        <v>-13.69</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-2.78</v>
+        <v>-27.8</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-3.05</v>
+        <v>-30.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:27</t>
+    <t xml:space="preserve">2026-10-04 08:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:18</t>
+    <t xml:space="preserve">2026-10-05 08:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
